--- a/Data/Excel/Hunting.xlsx
+++ b/Data/Excel/Hunting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ProjectBB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636B82F8-D4EF-4E94-9781-F41BEE37FA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D2374-A0CC-4E0F-9917-D5DCE0DD1D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="3684" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -101,10 +101,6 @@
     <t>drop_id</t>
   </si>
   <si>
-    <t>string[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{drop1;drop2;drop3;drop4;drop5}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -114,6 +110,14 @@
   </si>
   <si>
     <t>{drop1;drop2;drop3}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id[]:Drop</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +540,7 @@
     </row>
     <row r="2" spans="1:6" ht="13.8" thickBot="1">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -551,7 +555,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="35.4" thickBot="1">
@@ -571,7 +575,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="35.4" thickBot="1">
@@ -591,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
@@ -611,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
@@ -657,5 +661,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>